--- a/src/utils/sxsyzlzq/friends/taotailang/zz_taotailang_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/taotailang/zz_taotailang_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10725" windowHeight="11385" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="13500" windowHeight="10245" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="蛮石" sheetId="8" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="60">
   <si>
     <t>名称</t>
   </si>
@@ -40,6 +40,9 @@
     <t>卡等</t>
   </si>
   <si>
+    <t>愚笨鲸头鹅</t>
+  </si>
+  <si>
     <t>旷野祭师</t>
   </si>
   <si>
@@ -49,9 +52,6 @@
     <t>面包树</t>
   </si>
   <si>
-    <t>天降碎石</t>
-  </si>
-  <si>
     <t>强行捕猎</t>
   </si>
   <si>
@@ -79,9 +79,6 @@
     <t>飞斧狂人</t>
   </si>
   <si>
-    <t>飞斧女豪</t>
-  </si>
-  <si>
     <t>源力苏醒</t>
   </si>
   <si>
@@ -118,21 +115,18 @@
     <t>全数否定</t>
   </si>
   <si>
-    <t>学仆-魔蛛型</t>
-  </si>
-  <si>
     <t>学仆-能源型</t>
   </si>
   <si>
+    <t>隐形术</t>
+  </si>
+  <si>
     <t>破魔系教授</t>
   </si>
   <si>
     <t>克隆术</t>
   </si>
   <si>
-    <t>传记·海市蜃楼·蛇</t>
-  </si>
-  <si>
     <t>魔像-御咒铁卫</t>
   </si>
   <si>
@@ -154,12 +148,12 @@
     <t>魔像-钢翼仲裁者</t>
   </si>
   <si>
-    <t>No.4希尔伯特</t>
-  </si>
-  <si>
     <t>No.2时光·米拉</t>
   </si>
   <si>
+    <t>No.6迪宁</t>
+  </si>
+  <si>
     <t>No.6沃凡瑞拉</t>
   </si>
   <si>
@@ -181,19 +175,16 @@
     <t>连击</t>
   </si>
   <si>
+    <t>执剑道者</t>
+  </si>
+  <si>
     <t>龟族僧人</t>
   </si>
   <si>
-    <t>叶幻师</t>
-  </si>
-  <si>
     <t>铁山靠</t>
   </si>
   <si>
     <t>风卷残云</t>
-  </si>
-  <si>
-    <t>驱魔道人</t>
   </si>
   <si>
     <t>御风武者</t>
@@ -1208,18 +1199,18 @@
         <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1230,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1238,10 +1229,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1252,7 +1243,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1285,7 +1276,7 @@
       </c>
       <c r="C10" s="1">
         <f>AVERAGE(C2:C7)</f>
-        <v>19</v>
+        <v>18.8333333333333</v>
       </c>
       <c r="D10" s="2"/>
     </row>
@@ -1297,7 +1288,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1308,7 +1299,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1324,51 +1315,51 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="2">
         <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="2">
         <v>3</v>
       </c>
       <c r="C17" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="2">
+        <v>3</v>
+      </c>
+      <c r="C18" s="2">
         <v>15</v>
-      </c>
-      <c r="B18" s="2">
-        <v>4</v>
-      </c>
-      <c r="C18" s="2">
-        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="2">
         <v>6</v>
@@ -1379,13 +1370,13 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" s="2">
         <v>8</v>
       </c>
       <c r="C21" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1403,16 +1394,16 @@
         <v>8</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C24" s="2">
         <f>AVERAGE(C13:C21)</f>
-        <v>17.7777777777778</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B27" s="3">
         <v>3</v>
@@ -1423,7 +1414,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B28" s="3">
         <v>5</v>
@@ -1434,24 +1425,24 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B29" s="3">
         <v>7</v>
       </c>
       <c r="C29" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B30" s="3">
         <v>8</v>
       </c>
       <c r="C30" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1469,23 +1460,23 @@
         <v>8</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C33" s="3">
         <f>AVERAGE(C27:C30)</f>
-        <v>15.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="C36" s="4">
         <f>AVERAGE(C2:C7,C13:C21,C27:C30)</f>
-        <v>17.6842105263158</v>
+        <v>17.8421052631579</v>
       </c>
     </row>
   </sheetData>
@@ -1497,7 +1488,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="17.75" customWidth="1"/>
@@ -1518,7 +1509,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -1529,85 +1520,85 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="1">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
-        <v>22</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="1">
-        <f>AVERAGE(C2:C6)</f>
-        <v>17</v>
-      </c>
-      <c r="D9" s="2"/>
+      <c r="C8" s="1">
+        <f>AVERAGE(C2:C5)</f>
+        <v>17.5</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="2">
         <v>2</v>
@@ -1618,91 +1609,85 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2">
         <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C17" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B18" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2">
         <v>7</v>
       </c>
       <c r="C19" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C20" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="2">
-        <v>9</v>
-      </c>
-      <c r="C21" s="2">
-        <v>16</v>
-      </c>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2"/>
@@ -1710,28 +1695,34 @@
       <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="2" t="s">
+      <c r="A23" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" s="2">
-        <f>AVERAGE(C12:C21)</f>
-        <v>16.7</v>
+      <c r="B23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="2">
+        <f>AVERAGE(C11:C20)</f>
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="3">
+        <v>5</v>
+      </c>
+      <c r="C26" s="3">
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C27" s="3">
         <v>14</v>
@@ -1739,10 +1730,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C28" s="3">
         <v>16</v>
@@ -1750,25 +1741,19 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B29" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C29" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="3">
-        <v>9</v>
-      </c>
-      <c r="C30" s="3">
-        <v>16</v>
-      </c>
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="3"/>
@@ -1776,32 +1761,27 @@
       <c r="C31" s="3"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="3" t="s">
+      <c r="A32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="3">
+        <f>AVERAGE(C26:C29)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C33" s="3">
-        <f>AVERAGE(C27:C30)</f>
-        <v>15.25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C36" s="4">
-        <f>AVERAGE(C2:C6,C12:C21,C27:C30)</f>
-        <v>16.4736842105263</v>
+      <c r="B35" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="4">
+        <f>AVERAGE(C2:C5,C11:C20,C26:C29)</f>
+        <v>16.7777777777778</v>
       </c>
     </row>
   </sheetData>
@@ -1813,7 +1793,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1834,7 +1814,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -1845,7 +1825,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -1856,7 +1836,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1867,18 +1847,18 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -1889,7 +1869,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -1900,7 +1880,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -1911,195 +1891,218 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B10" s="1">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="1">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="1">
+        <v>3</v>
+      </c>
+      <c r="C12" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="1">
         <v>4</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="1">
-        <f>AVERAGE(C2:C10)</f>
+      <c r="C16" s="1">
+        <f>AVERAGE(C2:C13)</f>
         <v>13</v>
       </c>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" s="2">
-        <v>3</v>
-      </c>
-      <c r="C16" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="2">
-        <v>4</v>
-      </c>
-      <c r="C17" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="2">
-        <v>4</v>
-      </c>
-      <c r="C18" s="2">
-        <v>12</v>
-      </c>
+      <c r="D16" s="2"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
       </c>
       <c r="C19" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B20" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
+      <c r="A21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="2">
+        <v>4</v>
+      </c>
+      <c r="C21" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
+      <c r="A22" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="2">
+        <v>5</v>
+      </c>
+      <c r="C22" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" s="2">
-        <f>AVERAGE(C16:C20)</f>
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26" s="3">
-        <v>3</v>
-      </c>
-      <c r="C26" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="3">
-        <v>4</v>
-      </c>
-      <c r="C27" s="3">
-        <v>12</v>
+      <c r="B25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="2">
+        <f>AVERAGE(C19:C22)</f>
+        <v>12.5</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B28" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
+      <c r="A29" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="3">
+        <v>4</v>
+      </c>
+      <c r="C29" s="3">
+        <v>13</v>
+      </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
+      <c r="A30" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="3">
+        <v>4</v>
+      </c>
+      <c r="C30" s="3">
+        <v>12</v>
+      </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="3">
+        <f>AVERAGE(C28:C30)</f>
+        <v>12.3333333333333</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C31" s="3">
-        <f>AVERAGE(C26:C28)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C34" s="4">
-        <f>AVERAGE(C2:C10,C16:C20,C26:C28)</f>
-        <v>12.7647058823529</v>
+      <c r="B36" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="4">
+        <f>AVERAGE(C2:C13,C19:C22,C28:C30)</f>
+        <v>12.7894736842105</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>